--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488273_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488273_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2172</v>
+        <v>1.9732</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1436</v>
+        <v>0.7519</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0736</v>
+        <v>1.2214</v>
       </c>
       <c r="G3" t="n">
         <v>1.0742</v>
@@ -688,13 +688,13 @@
         <v>1.1117</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0313</v>
+        <v>-0.2126</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2699</v>
+        <v>-0.1219</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2385</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9651999999999999</v>
+        <v>1.4537</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1512</v>
+        <v>1.8367</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.186</v>
+        <v>-0.3829</v>
       </c>
       <c r="G4" t="n">
         <v>2.7337</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4895</v>
+        <v>-0.0009</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.2709</v>
+        <v>-0.5854</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7814</v>
+        <v>0.5844</v>
       </c>
       <c r="V4" t="n">
         <v>0.9444</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5317</v>
+        <v>0.5804</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6972</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2289</v>
+        <v>1.1796</v>
       </c>
       <c r="G6" t="n">
         <v>1.198</v>
@@ -922,13 +922,13 @@
         <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1845</v>
+        <v>-0.1359</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0204</v>
+        <v>-0.0696</v>
       </c>
       <c r="V6" t="n">
         <v>0.63</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8464</v>
+        <v>-0.5269</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2158</v>
+        <v>-1.1178</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3693</v>
+        <v>0.5909</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1859</v>
@@ -1000,13 +1000,13 @@
         <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6606</v>
+        <v>-0.341</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4166</v>
+        <v>-0.3186</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.244</v>
+        <v>-0.0224</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2248</v>
+        <v>-1.8628</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1205</v>
+        <v>-2.5122</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8956</v>
+        <v>0.6494</v>
       </c>
       <c r="G8" t="n">
         <v>0.521</v>
@@ -1078,13 +1078,13 @@
         <v>2.2234</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8841</v>
+        <v>0.2462</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3967</v>
+        <v>0.005</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4874</v>
+        <v>0.2412</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8888</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3816</v>
+        <v>-2.4134</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0533</v>
+        <v>-2.445</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6717</v>
+        <v>0.0315</v>
       </c>
       <c r="G9" t="n">
         <v>-3.8114</v>
@@ -1156,13 +1156,13 @@
         <v>1.8529</v>
       </c>
       <c r="S9" t="n">
-        <v>0.874</v>
+        <v>-0.1579</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2873</v>
+        <v>-0.1044</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5867</v>
+        <v>-0.0535</v>
       </c>
       <c r="V9" t="n">
         <v>0.6294</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3373</v>
+        <v>-3.1895</v>
       </c>
       <c r="E10" t="n">
         <v>-1.9673</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3699</v>
+        <v>-1.2222</v>
       </c>
       <c r="G10" t="n">
         <v>-0.348</v>
@@ -1234,13 +1234,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7309</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>-0.4924</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2385</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8877</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9108</v>
+        <v>-3.5426</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2993</v>
+        <v>-2.1034</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6115</v>
+        <v>-1.4392</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8841</v>
@@ -1312,13 +1312,13 @@
         <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6387</v>
+        <v>-0.2705</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3619</v>
+        <v>-0.166</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2768</v>
+        <v>-0.1045</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5733</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4481</v>
+        <v>-4.1537</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.6918</v>
+        <v>-3.4959</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7563</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9409</v>
@@ -1390,13 +1390,13 @@
         <v>1.1117</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0249</v>
+        <v>-0.7306</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5807</v>
+        <v>-0.3849</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4442</v>
+        <v>-0.3457</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6294</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6339</v>
+        <v>-4.7799</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5834</v>
+        <v>-1.8772</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0505</v>
+        <v>-2.9027</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2996</v>
@@ -1468,13 +1468,13 @@
         <v>1.4823</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1283</v>
+        <v>-0.0177</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2537</v>
+        <v>-0.0401</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1254</v>
+        <v>0.0224</v>
       </c>
       <c r="V13" t="n">
         <v>-2.8332</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-9.002800000000001</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.8385</v>
+        <v>-8.6426</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1643</v>
+        <v>0.0326</v>
       </c>
       <c r="G14" t="n">
         <v>-7.8256</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8623</v>
+        <v>-0.4694</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4203</v>
+        <v>-0.2244</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.442</v>
+        <v>-0.245</v>
       </c>
       <c r="V14" t="n">
         <v>-0.315</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-21.273</v>
+        <v>-21.2729</v>
       </c>
       <c r="E15" t="n">
-        <v>-18.3737</v>
+        <v>-18.3735</v>
       </c>
       <c r="F15" t="n">
         <v>-2.8994</v>
@@ -1624,13 +1624,13 @@
         <v>14.8229</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.6737</v>
+        <v>-2.6735</v>
       </c>
       <c r="T15" t="n">
         <v>-2.4993</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1742999999999998</v>
+        <v>-0.1742999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-6.9236</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>8.129200000000001</v>
+        <v>8.5771</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5149</v>
+        <v>5.0046</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6143</v>
+        <v>3.5725</v>
       </c>
       <c r="G16" t="n">
         <v>4.1894</v>
@@ -1702,13 +1702,13 @@
         <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2629</v>
+        <v>0.185</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6019</v>
+        <v>-0.1122</v>
       </c>
       <c r="U16" t="n">
-        <v>0.339</v>
+        <v>0.2972</v>
       </c>
       <c r="V16" t="n">
         <v>3.4616</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>M. EZOMO GERVILLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.7289</v>
+        <v>4.056</v>
       </c>
       <c r="E17" t="n">
-        <v>2.154</v>
+        <v>0.3908</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5748</v>
+        <v>3.6652</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.9393</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4588</v>
+        <v>0.1898</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5268</v>
+        <v>1.7496</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2217</v>
+        <v>0.0475</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8331</v>
+        <v>-0.0047</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.0522</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2897</v>
+        <v>1.8919</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3743</v>
+        <v>0.1944</v>
       </c>
       <c r="O17" t="n">
-        <v>0.08459999999999999</v>
+        <v>1.6974</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>2.981</v>
+        <v>0.3199</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1737</v>
+        <v>0.0289</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8073</v>
+        <v>0.291</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.3144</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.315</v>
+        <v>0.3144</v>
       </c>
       <c r="X17" t="n">
-        <v>0.9455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3125</v>
+        <v>3.9539</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0265</v>
+        <v>2.4389</v>
       </c>
       <c r="F18" t="n">
-        <v>1.286</v>
+        <v>1.515</v>
       </c>
       <c r="G18" t="n">
         <v>3.5716</v>
@@ -1858,13 +1858,13 @@
         <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6302</v>
+        <v>0.2717</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5397</v>
+        <v>-0.0479</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0905</v>
+        <v>0.3196</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6304999999999999</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2438</v>
+        <v>3.6682</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3971</v>
+        <v>-0.1033</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6409</v>
+        <v>3.7715</v>
       </c>
       <c r="G19" t="n">
         <v>1.3238</v>
@@ -1936,13 +1936,13 @@
         <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.4915</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1131</v>
+        <v>0.1806</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1803</v>
+        <v>0.3109</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. EZOMO GERVILLA</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.166</v>
+        <v>3.0532</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2947</v>
+        <v>0.6851</v>
       </c>
       <c r="F20" t="n">
-        <v>3.4607</v>
+        <v>2.3682</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9393</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1898</v>
+        <v>1.4588</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7496</v>
+        <v>-0.5268</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0475</v>
+        <v>1.2217</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0047</v>
+        <v>1.8331</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0522</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>1.8919</v>
+        <v>-0.2897</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1944</v>
+        <v>-0.3743</v>
       </c>
       <c r="O20" t="n">
-        <v>1.6974</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4823</v>
+        <v>0.1853</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.57</v>
+        <v>1.3054</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6566</v>
+        <v>0.7048</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.6006</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3144</v>
+        <v>0.6304999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>-0.315</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.9455</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.7743</v>
+        <v>2.8075</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6319</v>
+        <v>2.436</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1424</v>
+        <v>0.3715</v>
       </c>
       <c r="G21" t="n">
         <v>1.0034</v>
@@ -2092,13 +2092,13 @@
         <v>2.2234</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4143</v>
+        <v>-0.3811</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1131</v>
+        <v>-0.309</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3012</v>
+        <v>-0.0721</v>
       </c>
       <c r="V21" t="n">
         <v>1.2589</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4065</v>
+        <v>1.4073</v>
       </c>
       <c r="E22" t="n">
-        <v>1.3875</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.019</v>
+        <v>2.3645</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9913</v>
+        <v>3.4699</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4062</v>
+        <v>2.9875</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5851</v>
+        <v>0.4825</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4036</v>
+        <v>3.3587</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5455</v>
+        <v>3.3066</v>
       </c>
       <c r="L22" t="n">
-        <v>1.9492</v>
+        <v>0.0522</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.395</v>
+        <v>0.1112</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1393</v>
+        <v>-0.3191</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.5343</v>
+        <v>0.4303</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1117</v>
+        <v>-3.7057</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-5.7439</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2861</v>
+        <v>0.3843</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5397</v>
+        <v>0.1691</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7464</v>
+        <v>0.2151</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6142</v>
+        <v>0.5068</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3489</v>
+        <v>0.702</v>
       </c>
       <c r="F23" t="n">
-        <v>1.963</v>
+        <v>-0.1952</v>
       </c>
       <c r="G23" t="n">
-        <v>3.4699</v>
+        <v>-0.9913</v>
       </c>
       <c r="H23" t="n">
-        <v>2.9875</v>
+        <v>-0.4062</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4825</v>
+        <v>-0.5851</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3587</v>
+        <v>1.4036</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3066</v>
+        <v>-0.5455</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0522</v>
+        <v>1.9492</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1112</v>
+        <v>-2.395</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3191</v>
+        <v>0.1393</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4303</v>
+        <v>-2.5343</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.7057</v>
+        <v>1.1117</v>
       </c>
       <c r="Q23" t="n">
-        <v>-5.7439</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0382</v>
+        <v>1.6676</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4089</v>
+        <v>0.3864</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2226</v>
+        <v>-0.1458</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1863</v>
+        <v>0.5322</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8441</v>
+        <v>-0.5738</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0432</v>
+        <v>-0.9453</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1991</v>
+        <v>0.3714</v>
       </c>
       <c r="G24" t="n">
         <v>0.0878</v>
@@ -2326,13 +2326,13 @@
         <v>0.9264</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3089</v>
+        <v>0.5792</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3246</v>
+        <v>0.4225</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0157</v>
+        <v>0.1567</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3144</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>J. PONCE GONZALEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.3849</v>
+        <v>-1.2371</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0459</v>
+        <v>-2.6773</v>
       </c>
       <c r="F25" t="n">
-        <v>1.661</v>
+        <v>1.4402</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.8946</v>
+        <v>-2.0051</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.9945</v>
+        <v>0.6384</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9001</v>
+        <v>-2.6435</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.4426</v>
+        <v>-1.1154</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.5256</v>
+        <v>0.1074</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0829</v>
+        <v>-1.2228</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.452</v>
+        <v>-0.8897</v>
       </c>
       <c r="N25" t="n">
         <v>0.531</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.983</v>
+        <v>-1.4207</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.3706</v>
+        <v>-1.297</v>
       </c>
       <c r="R25" t="n">
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2688</v>
+        <v>0.138</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5471</v>
+        <v>-0.2649</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.4029</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3144</v>
+        <v>0.63</v>
       </c>
       <c r="W25" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. PONCE GONZALEZ</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.0795</v>
+        <v>-1.3127</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.069</v>
+        <v>-2.7521</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9895</v>
+        <v>1.4394</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.0051</v>
+        <v>-2.8946</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6384</v>
+        <v>-1.9945</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.6435</v>
+        <v>-0.9001</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.1154</v>
+        <v>-2.4426</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1074</v>
+        <v>-2.5256</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.2228</v>
+        <v>0.0829</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8897</v>
+        <v>-0.452</v>
       </c>
       <c r="N26" t="n">
         <v>0.531</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.4207</v>
+        <v>-0.983</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.297</v>
+        <v>-0.3706</v>
       </c>
       <c r="R26" t="n">
         <v>1.297</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7043</v>
+        <v>0.341</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6566</v>
+        <v>-0.2534</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0478</v>
+        <v>0.5944</v>
       </c>
       <c r="V26" t="n">
-        <v>0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X26" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.7938</v>
+        <v>-2.3277</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.6167</v>
+        <v>-1.323</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.1771</v>
+        <v>-1.0047</v>
       </c>
       <c r="G27" t="n">
         <v>-2.6563</v>
@@ -2560,13 +2560,13 @@
         <v>0.9264</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5081</v>
+        <v>-0.042</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4924</v>
+        <v>-0.1986</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0157</v>
+        <v>0.1567</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>21.2731</v>
+        <v>22.5787</v>
       </c>
       <c r="E28" t="n">
-        <v>2.899299999999999</v>
+        <v>2.899200000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>18.3736</v>
+        <v>19.6795</v>
       </c>
       <c r="G28" t="n">
         <v>7.969899999999999</v>
@@ -2629,7 +2629,7 @@
         <v>-6.2578</v>
       </c>
       <c r="P28" t="n">
-        <v>3.7057</v>
+        <v>3.705699999999999</v>
       </c>
       <c r="Q28" t="n">
         <v>-14.823</v>
@@ -2638,13 +2638,13 @@
         <v>18.5287</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6736</v>
+        <v>3.9793</v>
       </c>
       <c r="T28" t="n">
-        <v>0.1743000000000002</v>
+        <v>0.1741</v>
       </c>
       <c r="U28" t="n">
-        <v>2.4993</v>
+        <v>3.8052</v>
       </c>
       <c r="V28" t="n">
         <v>6.923799999999999</v>
